--- a/data_with_qrdemo_highlighted.xlsx
+++ b/data_with_qrdemo_highlighted.xlsx
@@ -945,11 +945,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Scanned 3 Times</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
     </row>
     <row r="3" ht="75" customHeight="1">
@@ -982,11 +978,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Scanned</t>
-        </is>
-      </c>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
     </row>
     <row r="4" ht="75" customHeight="1">
